--- a/data/trans_bre/P19C02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,35</t>
+          <t>-4,59; 3,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,49</t>
+          <t>2,21; 9,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 9,58</t>
+          <t>0,18; 9,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 13,89</t>
+          <t>5,04; 14,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 23,16</t>
+          <t>-23,45; 22,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,96; 70,21</t>
+          <t>13,02; 72,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 53,34</t>
+          <t>-0,22; 54,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,02; 72,29</t>
+          <t>19,82; 72,21</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 6,86</t>
+          <t>-0,84; 6,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,76</t>
+          <t>-1,15; 5,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,47</t>
+          <t>1,06; 8,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 26,57</t>
+          <t>-0,18; 28,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 23,47</t>
+          <t>-2,59; 22,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 18,02</t>
+          <t>-3,36; 18,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 22,27</t>
+          <t>2,82; 24,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 77,79</t>
+          <t>-0,33; 83,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 9,22</t>
+          <t>-3,71; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 6,94</t>
+          <t>-6,65; 7,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,51</t>
+          <t>-8,85; 4,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,95</t>
+          <t>-7,39; 3,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 24,59</t>
+          <t>-8,62; 27,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 18,43</t>
+          <t>-15,26; 20,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 10,34</t>
+          <t>-17,47; 9,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 5,29</t>
+          <t>-11,9; 5,51</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,19</t>
+          <t>-2,11; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,96</t>
+          <t>-0,64; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,07</t>
+          <t>-0,35; 5,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 19,65</t>
+          <t>0,18; 19,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 11,65</t>
+          <t>-6,98; 10,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 13,92</t>
+          <t>-2,06; 15,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 15,21</t>
+          <t>-0,96; 14,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 53,47</t>
+          <t>0,3; 54,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C02-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,41</t>
+          <t>-3,98; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,52</t>
+          <t>2,09; 9,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,86</t>
+          <t>-0,21; 9,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 14,05</t>
+          <t>5,55; 14,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 22,88</t>
+          <t>-21,03; 22,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,02; 72,7</t>
+          <t>11,36; 69,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 54,29</t>
+          <t>-1,01; 54,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 72,21</t>
+          <t>21,95; 70,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,47</t>
+          <t>-0,89; 6,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,92</t>
+          <t>-0,96; 5,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,16</t>
+          <t>1,0; 7,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 28,02</t>
+          <t>-0,82; 5,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 22,5</t>
+          <t>-2,66; 21,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 18,48</t>
+          <t>-3,08; 18,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 24,79</t>
+          <t>2,8; 22,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 83,95</t>
+          <t>-1,59; 11,91</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,14%</t>
+          <t>-4,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 9,96</t>
+          <t>-3,38; 10,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 7,7</t>
+          <t>-6,8; 7,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 4,35</t>
+          <t>-9,35; 3,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 3,15</t>
+          <t>-7,85; 2,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 27,26</t>
+          <t>-7,67; 28,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 20,73</t>
+          <t>-15,2; 20,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 9,88</t>
+          <t>-18,47; 8,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 5,51</t>
+          <t>-12,62; 4,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,9</t>
+          <t>-1,9; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,25</t>
+          <t>-0,66; 4,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,05</t>
+          <t>-0,15; 4,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 19,17</t>
+          <t>-0,74; 4,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 10,64</t>
+          <t>-6,44; 11,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 15,02</t>
+          <t>-2,15; 14,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 14,96</t>
+          <t>-0,44; 14,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 54,9</t>
+          <t>-1,54; 8,81</t>
         </is>
       </c>
     </row>
